--- a/diseases/d094/1995-1999.xlsx
+++ b/diseases/d094/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>745</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>643</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>429</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>600</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>705</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>602</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>583</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>752</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>786</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>811</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>816</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>560</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>684</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>647</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>602</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>690</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>740</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>619</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>768</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>828</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>808</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>862</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>774</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>674</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>887</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11068,9 +10993,6 @@
       <c r="O54" t="n">
         <v>758</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11700,9 +11622,6 @@
       <c r="O57" t="n">
         <v>708</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12332,9 +12251,6 @@
       <c r="O60" t="n">
         <v>793</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12964,9 +12880,6 @@
       <c r="O63" t="n">
         <v>726</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="S63" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13596,9 +13509,6 @@
       <c r="O66" t="n">
         <v>699</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14228,9 +14138,6 @@
       <c r="O69" t="n">
         <v>847</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14860,9 +14767,6 @@
       <c r="O72" t="n">
         <v>839</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15492,9 +15396,6 @@
       <c r="O75" t="n">
         <v>927</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="S75" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16124,9 +16025,6 @@
       <c r="O78" t="n">
         <v>863</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16756,9 +16654,6 @@
       <c r="O81" t="n">
         <v>822</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="S81" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17388,9 +17283,6 @@
       <c r="O84" t="n">
         <v>774</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18020,9 +17912,6 @@
       <c r="O87" t="n">
         <v>903</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="S87" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18891,9 +18780,6 @@
       <c r="O91" t="n">
         <v>776</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="S91" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19523,9 +19409,6 @@
       <c r="O94" t="n">
         <v>910</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20155,9 +20038,6 @@
       <c r="O97" t="n">
         <v>752</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20787,9 +20667,6 @@
       <c r="O100" t="n">
         <v>765</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21419,9 +21296,6 @@
       <c r="O103" t="n">
         <v>808</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22051,9 +21925,6 @@
       <c r="O106" t="n">
         <v>912</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22683,9 +22554,6 @@
       <c r="O109" t="n">
         <v>1012</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23315,9 +23183,6 @@
       <c r="O112" t="n">
         <v>1009</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23947,9 +23812,6 @@
       <c r="O115" t="n">
         <v>1005</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24579,9 +24441,6 @@
       <c r="O118" t="n">
         <v>899</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25211,9 +25070,6 @@
       <c r="O121" t="n">
         <v>913</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25843,9 +25699,6 @@
       <c r="O124" t="n">
         <v>846</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26714,9 +26567,6 @@
       <c r="O128" t="n">
         <v>796</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27346,9 +27196,6 @@
       <c r="O131" t="n">
         <v>917</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27978,9 +27825,6 @@
       <c r="O134" t="n">
         <v>776</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28610,9 +28454,6 @@
       <c r="O137" t="n">
         <v>859</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29242,9 +29083,6 @@
       <c r="O140" t="n">
         <v>708</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29874,9 +29712,6 @@
       <c r="O143" t="n">
         <v>842</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30506,9 +30341,6 @@
       <c r="O146" t="n">
         <v>1053</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31138,9 +30970,6 @@
       <c r="O149" t="n">
         <v>1097</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="S149" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31770,9 +31599,6 @@
       <c r="O152" t="n">
         <v>929</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32402,9 +32228,6 @@
       <c r="O155" t="n">
         <v>998</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33033,9 +32856,6 @@
       </c>
       <c r="O158" t="n">
         <v>834</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
